--- a/data/trans_camb/IP1012-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Edad-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,88</t>
+          <t>-0,5; 0,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,24; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,44</t>
+          <t>-1,25; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,24</t>
+          <t>-1,88; 0,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,95</t>
+          <t>-0,65; 0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,15</t>
+          <t>-1,04; 0,14</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,75</t>
+          <t>-2,41; 0,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,33</t>
+          <t>-2,86; 0,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,29</t>
+          <t>-0,93; 1,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,16</t>
+          <t>-1,27; 0,25</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,48</t>
+          <t>-1,09; 2,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,0</t>
+          <t>-2,34; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,47</t>
+          <t>-1,94; 1,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,67</t>
+          <t>-2,23; 1,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,32</t>
+          <t>-1,09; 1,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,44</t>
+          <t>-1,64; 0,44</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,36; 366,29</t>
+          <t>-79,46; 366,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 299,54</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,85</t>
+          <t>-0,38; 0,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; -0,09</t>
+          <t>-0,8; -0,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,85</t>
+          <t>-0,76; 0,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,17</t>
+          <t>-1,17; 0,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,6</t>
+          <t>-0,35; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; -0,0</t>
+          <t>-0,82; -0,06</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 197,79</t>
+          <t>-66,91; 233,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-90,71; 59,63</t>
+          <t>-90,24; 66,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 186,79</t>
+          <t>-48,92; 185,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-91,69; 26,51</t>
+          <t>-92,2; 12,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Edad-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,88</t>
+          <t>-0,5; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,0</t>
+          <t>-1,36; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,56</t>
+          <t>-1,23; 1,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,25</t>
+          <t>-1,84; 0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,95</t>
+          <t>-0,75; 0,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,14</t>
+          <t>-1,05; 0,14</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,72</t>
+          <t>-2,36; 0,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,39</t>
+          <t>-2,74; 0,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,08</t>
+          <t>-0,96; 0,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,25</t>
+          <t>-1,31; 0,25</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,36</t>
+          <t>-1,06; 2,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,78</t>
+          <t>-1,98; 1,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,47</t>
+          <t>-2,19; 1,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,36</t>
+          <t>-0,98; 1,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,44</t>
+          <t>-1,68; 0,42</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,46; 366,82</t>
+          <t>-76,27; 374,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 299,54</t>
+          <t>-100,0; 415,76</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,8</t>
+          <t>-0,35; 0,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; -0,09</t>
+          <t>-0,83; -0,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,86</t>
+          <t>-0,81; 0,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,12</t>
+          <t>-1,14; 0,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,61</t>
+          <t>-0,39; 0,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; -0,06</t>
+          <t>-0,79; -0,05</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 793,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 233,53</t>
+          <t>-71,01; 183,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-90,24; 66,22</t>
+          <t>-89,86; 62,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 185,47</t>
+          <t>-56,36; 167,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-92,2; 12,04</t>
+          <t>-91,87; 20,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,03</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,08</t>
+          <t>-1,28; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,0</t>
+          <t>-1,87; 0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,51</t>
+          <t>-0,51; 0,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,24</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,88</t>
+          <t>-0,72; 0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,14</t>
+          <t>-0,95; 0,15</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-3,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-68,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>11,78%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,74%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-68,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,59</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>-2,37; 0,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,43; 0,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,73</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,96</t>
+          <t>-0,76; 1,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,25</t>
+          <t>-1,56; 0,16</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-56,26%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-64,14%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-56,26%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-64,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,79</t>
+          <t>-2,14; 1,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-1,97; 1,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,61</t>
+          <t>-1,0; 2,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,36</t>
+          <t>-2,21; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,36</t>
+          <t>-1,08; 1,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,42</t>
+          <t>-1,61; 0,44</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-5,85%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-26,58%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>37,71%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-5,85%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-26,58%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 374,34</t>
+          <t>-80,36; 366,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 415,76</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,29</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,73</t>
+          <t>-0,75; 0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; -0,09</t>
+          <t>-1,15; 0,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,76</t>
+          <t>-0,27; 0,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,16</t>
+          <t>-0,81; -0,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,58</t>
+          <t>-0,37; 0,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; -0,05</t>
+          <t>-0,74; -0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-53,34%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>55,52%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-53,34%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 793,42</t>
+          <t>-70,0; 197,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,71; 59,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 183,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 62,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 167,91</t>
+          <t>-51,11; 186,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-91,87; 20,78</t>
+          <t>-91,69; 26,51</t>
         </is>
       </c>
     </row>
